--- a/artfynd/A 49977-2023 artfynd.xlsx
+++ b/artfynd/A 49977-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49977-2023 artfynd.xlsx
+++ b/artfynd/A 49977-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112243356</v>
+        <v>123803387</v>
       </c>
       <c r="B2" t="n">
-        <v>56461</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stalons kalkgranskog, Ås lm</t>
+          <t>Stalon, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540493</v>
+        <v>540013</v>
       </c>
       <c r="R2" t="n">
-        <v>7201782</v>
+        <v>7202083</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,16 +770,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,17 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isak Vahlström, Sara Forsström </t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112243375</v>
+        <v>112243356</v>
       </c>
       <c r="B3" t="n">
-        <v>90876</v>
+        <v>56461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,41 +798,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540492</v>
+        <v>540493</v>
       </c>
       <c r="R3" t="n">
-        <v>7201745</v>
+        <v>7201782</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -928,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112243351</v>
+        <v>112243375</v>
       </c>
       <c r="B4" t="n">
-        <v>56461</v>
+        <v>90876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,33 +925,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -1027,6 +1010,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1055,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112331142</v>
+        <v>112243351</v>
       </c>
       <c r="B5" t="n">
-        <v>73873</v>
+        <v>56461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,34 +1055,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stalon, Ås lm</t>
+          <t>Stalons kalkgranskog, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540670</v>
+        <v>540492</v>
       </c>
       <c r="R5" t="n">
-        <v>7201629</v>
+        <v>7201745</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1125,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,26 +1140,36 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t xml:space="preserve">Isak Vahlström, Sara Forsström </t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112331159</v>
+        <v>112331142</v>
       </c>
       <c r="B6" t="n">
-        <v>89979</v>
+        <v>73873</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,16 +1182,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1274,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112331143</v>
+        <v>112331159</v>
       </c>
       <c r="B7" t="n">
-        <v>73873</v>
+        <v>89979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,21 +1294,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1314,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540640</v>
+        <v>540670</v>
       </c>
       <c r="R7" t="n">
-        <v>7201674</v>
+        <v>7201629</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1349,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112331150</v>
+        <v>112331143</v>
       </c>
       <c r="B8" t="n">
-        <v>78753</v>
+        <v>73873</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,21 +1401,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540698</v>
+        <v>540640</v>
       </c>
       <c r="R8" t="n">
-        <v>7201616</v>
+        <v>7201674</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112331168</v>
+        <v>112331150</v>
       </c>
       <c r="B9" t="n">
-        <v>78785</v>
+        <v>78753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1509,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540707</v>
+        <v>540698</v>
       </c>
       <c r="R9" t="n">
-        <v>7201617</v>
+        <v>7201616</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,6 +1606,118 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112331168</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78785</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>540707</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7201617</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49977-2023 artfynd.xlsx
+++ b/artfynd/A 49977-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123803387</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2023 artfynd.xlsx
+++ b/artfynd/A 49977-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123803387</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49977-2023 artfynd.xlsx
+++ b/artfynd/A 49977-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123803387</v>
+        <v>130581332</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,27 +705,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stalon, Stalon, Ås lm</t>
+          <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540013</v>
+        <v>539511</v>
       </c>
       <c r="R2" t="n">
-        <v>7202083</v>
+        <v>7202207</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,55 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112243356</v>
+        <v>112243363</v>
       </c>
       <c r="B3" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540493</v>
+        <v>540400</v>
       </c>
       <c r="R3" t="n">
-        <v>7201782</v>
+        <v>7201915</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +901,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isak Vahlström, Sara Forsström </t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112243375</v>
+        <v>123803387</v>
       </c>
       <c r="B4" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,40 +919,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stalons kalkgranskog, Ås lm</t>
+          <t>Stalon, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540492</v>
+        <v>540013</v>
       </c>
       <c r="R4" t="n">
-        <v>7201745</v>
+        <v>7202083</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,19 +996,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,62 +1007,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isak Vahlström, Sara Forsström </t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112243351</v>
+        <v>112331147</v>
       </c>
       <c r="B5" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stalons kalkgranskog, Ås lm</t>
+          <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540492</v>
+        <v>540526</v>
       </c>
       <c r="R5" t="n">
-        <v>7201745</v>
+        <v>7201969</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,22 +1079,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,63 +1105,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isak Vahlström, Sara Forsström </t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112331142</v>
+        <v>112331167</v>
       </c>
       <c r="B6" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540670</v>
+        <v>540533</v>
       </c>
       <c r="R6" t="n">
-        <v>7201629</v>
+        <v>7201972</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,15 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112331159</v>
+        <v>112243375</v>
       </c>
       <c r="B7" t="n">
-        <v>89979</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,29 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>5964</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stalon, Ås lm</t>
+          <t>Stalons kalkgranskog, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540670</v>
+        <v>540491</v>
       </c>
       <c r="R7" t="n">
-        <v>7201629</v>
+        <v>7201745</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1343,22 +1296,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,33 +1320,39 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112331143</v>
+        <v>112243351</v>
       </c>
       <c r="B8" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,34 +1360,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stalon, Ås lm</t>
+          <t>Stalons kalkgranskog, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540640</v>
+        <v>540491</v>
       </c>
       <c r="R8" t="n">
-        <v>7201674</v>
+        <v>7201745</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1455,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,31 +1445,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112331150</v>
+        <v>112243352</v>
       </c>
       <c r="B9" t="n">
-        <v>78753</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,34 +1482,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stalon, Ås lm</t>
+          <t>Stalons kalkgranskog, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540698</v>
+        <v>540456</v>
       </c>
       <c r="R9" t="n">
-        <v>7201616</v>
+        <v>7201763</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1567,22 +1541,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,66 +1567,76 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112331168</v>
+        <v>112243353</v>
       </c>
       <c r="B10" t="n">
-        <v>78785</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stalon, Ås lm</t>
+          <t>Stalons kalkgranskog, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540707</v>
+        <v>540455</v>
       </c>
       <c r="R10" t="n">
-        <v>7201617</v>
+        <v>7201745</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,22 +1663,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,19 +1689,686 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112243356</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stalons kalkgranskog, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>540493</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7201782</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112331150</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>540698</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7201615</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Yasmine Kindlund</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112331142</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>540670</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7201629</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112331143</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>540640</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7201674</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112331168</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>540707</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7201618</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112331159</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>540670</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7201629</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
